--- a/task305/golden/marrable_site_appraisal_2027.xlsx
+++ b/task305/golden/marrable_site_appraisal_2027.xlsx
@@ -19,9 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="73">
-  <si>
-    <t>Open S3 Wrentoft, Mill Lane: it adds GBP 0.8 million a year, ahead of S1 Bellingtoft at GBP 0.5 million</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
+  <si>
+    <t>Open S3 Wrentoft, Mill Lane: it adds GBP 0.8 million a year, ahead of S1 Bellingtoft at GBP 0.4 million</t>
   </si>
   <si>
     <t>Site</t>
@@ -87,10 +87,10 @@
     <t>Brackenmere, Northfield</t>
   </si>
   <si>
-    <t>Addition = 26% of the store's sales, less 26% of the sales it takes from our ten stores, less its running costs (Finance's appraisal rule, spend-share model sheet). Sales include the guests of the region's holiday parks at GBP 2,440 a pitch a season; the residents-only column leaves them out.</t>
-  </si>
-  <si>
-    <t>Six pitch-measured sites on the 2026 rating list; Wrentoft Lakes is the largest</t>
+    <t>Addition = 26% of the store's sales, less 26% of the sales it takes from our ten stores, less its running costs (Finance's appraisal rule, spend-share model sheet). Sales include the guests of the region's holiday parks at GBP 2,480 a pitch a season; the residents-only column leaves them out.</t>
+  </si>
+  <si>
+    <t>Four pitch-measured sites on the 2026 rating list; Wrentoft Lakes is the largest</t>
   </si>
   <si>
     <t>Rating-list description</t>
@@ -105,34 +105,22 @@
     <t>Caravan Park and Premises</t>
   </si>
   <si>
-    <t>LQ15 4DZ</t>
-  </si>
-  <si>
-    <t>LQ18 4PH</t>
-  </si>
-  <si>
-    <t>LQ6 2DB</t>
-  </si>
-  <si>
-    <t>LQ16 1AR</t>
-  </si>
-  <si>
-    <t>Camping Site and Premises</t>
-  </si>
-  <si>
-    <t>LQ7 2AA</t>
-  </si>
-  <si>
-    <t>Touring Caravan Site and Premises</t>
-  </si>
-  <si>
-    <t>LQ17 1XA</t>
+    <t>LQ15 4UE</t>
+  </si>
+  <si>
+    <t>LQ18 4XA</t>
+  </si>
+  <si>
+    <t>LQ6 2HZ</t>
+  </si>
+  <si>
+    <t>LQ16 1NA</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>Guests' in-store spend: GBP 2,440 a pitch for a season, from the out-of-region card spend at our stores (March to October, above each store's November to February level, grossed up by its card share).</t>
+    <t>Guests' in-store spend: GBP 2,480 a pitch for a season, from the out-of-region card spend at our stores (March to October, above each store's November to February level, grossed up by its card share).</t>
   </si>
   <si>
     <t>Guests' spend at our stores, FY2025/26</t>
@@ -225,7 +213,7 @@
     <t>Stores in the share</t>
   </si>
   <si>
-    <t>24 grocery stores of 280 m2 or more on the 2026 rating list</t>
+    <t>27 grocery stores of 280 m2 or more on the 2026 rating list</t>
   </si>
   <si>
     <t>Running costs</t>
@@ -730,19 +718,19 @@
         <v>1500</v>
       </c>
       <c r="D4" s="4">
-        <v>7133923</v>
+        <v>6775669</v>
       </c>
       <c r="E4" s="4">
-        <v>289588</v>
+        <v>142674</v>
       </c>
       <c r="F4" s="4">
-        <v>976000</v>
+        <v>924000</v>
       </c>
       <c r="G4" s="4">
-        <v>803527</v>
+        <v>800579</v>
       </c>
       <c r="H4" s="4">
-        <v>144617</v>
+        <v>137306</v>
       </c>
       <c r="I4" s="5">
         <v>0.8</v>
@@ -759,22 +747,22 @@
         <v>1800</v>
       </c>
       <c r="D5" s="6">
-        <v>7639952</v>
+        <v>6753698</v>
       </c>
       <c r="E5" s="6">
-        <v>1071689</v>
+        <v>612067</v>
       </c>
       <c r="F5" s="6">
-        <v>1200000</v>
+        <v>1177000</v>
       </c>
       <c r="G5" s="6">
-        <v>507748</v>
+        <v>419824</v>
       </c>
       <c r="H5" s="6">
-        <v>496330</v>
+        <v>408667</v>
       </c>
       <c r="I5" s="7">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -788,19 +776,19 @@
         <v>1800</v>
       </c>
       <c r="D6" s="6">
-        <v>5640896</v>
+        <v>5235777</v>
       </c>
       <c r="E6" s="6">
-        <v>2065177</v>
+        <v>1759978</v>
       </c>
       <c r="F6" s="6">
         <v>839000</v>
       </c>
       <c r="G6" s="6">
-        <v>90687</v>
+        <v>64708</v>
       </c>
       <c r="H6" s="6">
-        <v>88946</v>
+        <v>63097</v>
       </c>
       <c r="I6" s="7">
         <v>0.1</v>
@@ -817,19 +805,19 @@
         <v>1500</v>
       </c>
       <c r="D7" s="6">
-        <v>5080937</v>
+        <v>3586357</v>
       </c>
       <c r="E7" s="6">
-        <v>2536058</v>
+        <v>1180141</v>
       </c>
       <c r="F7" s="6">
         <v>662000</v>
       </c>
       <c r="G7" s="6">
-        <v>-331</v>
+        <v>-36384</v>
       </c>
       <c r="H7" s="6">
-        <v>-10254</v>
+        <v>-51802</v>
       </c>
       <c r="I7" s="7">
         <v>0</v>
@@ -846,19 +834,19 @@
         <v>1600</v>
       </c>
       <c r="D8" s="6">
-        <v>4510917</v>
+        <v>4237684</v>
       </c>
       <c r="E8" s="6">
-        <v>2449016</v>
+        <v>2173497</v>
       </c>
       <c r="F8" s="6">
         <v>659000</v>
       </c>
       <c r="G8" s="6">
-        <v>-122906</v>
+        <v>-122311</v>
       </c>
       <c r="H8" s="6">
-        <v>-123799</v>
+        <v>-123247</v>
       </c>
       <c r="I8" s="7">
         <v>-0.1</v>
@@ -875,19 +863,19 @@
         <v>1500</v>
       </c>
       <c r="D9" s="6">
-        <v>4481202</v>
+        <v>4399247</v>
       </c>
       <c r="E9" s="6">
-        <v>2392827</v>
+        <v>2305168</v>
       </c>
       <c r="F9" s="6">
         <v>691000</v>
       </c>
       <c r="G9" s="6">
-        <v>-148023</v>
+        <v>-146540</v>
       </c>
       <c r="H9" s="6">
-        <v>-148190</v>
+        <v>-146675</v>
       </c>
       <c r="I9" s="7">
         <v>-0.1</v>
@@ -905,7 +893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -948,7 +936,7 @@
         <v>29</v>
       </c>
       <c r="C5" s="6">
-        <v>420</v>
+        <v>640</v>
       </c>
     </row>
     <row r="6">
@@ -959,7 +947,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="6">
-        <v>240</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7">
@@ -970,42 +958,20 @@
         <v>31</v>
       </c>
       <c r="C7" s="6">
-        <v>80</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="6">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C8" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1024,100 +990,100 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6">
-        <v>29833</v>
+        <v>12734</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6">
-        <v>2747</v>
+        <v>-474</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B6" s="6">
-        <v>8285</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" s="6">
-        <v>99411</v>
+        <v>62452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B8" s="6">
-        <v>328864</v>
+        <v>147547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B9" s="6">
-        <v>33646</v>
+        <v>-426</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B10" s="6">
-        <v>615358</v>
+        <v>285788</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="6">
-        <v>53583</v>
+        <v>17369</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6">
-        <v>10594</v>
+        <v>5389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B13" s="6">
-        <v>2496</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1136,100 +1102,100 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6">
-        <v>7456</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6">
-        <v>7085</v>
+        <v>6975</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B6" s="6">
-        <v>6968</v>
+        <v>6653</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" s="6">
-        <v>7290</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B8" s="6">
-        <v>5954</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B9" s="6">
-        <v>6734</v>
+        <v>6729</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B10" s="6">
-        <v>5710</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="6">
-        <v>4658</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6">
-        <v>3890</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B13" s="6">
-        <v>4429</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1248,20 +1214,20 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6">
         <v>1890</v>
@@ -1269,7 +1235,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6">
         <v>1608</v>
@@ -1277,7 +1243,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B6" s="6">
         <v>1488</v>
@@ -1285,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" s="6">
         <v>1401</v>
@@ -1293,7 +1259,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B8" s="6">
         <v>1194</v>
@@ -1301,7 +1267,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B9" s="6">
         <v>1259</v>
@@ -1309,7 +1275,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B10" s="6">
         <v>1248</v>
@@ -1317,7 +1283,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="6">
         <v>1052</v>
@@ -1325,7 +1291,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6">
         <v>822</v>
@@ -1333,7 +1299,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B13" s="6">
         <v>764</v>
@@ -1341,7 +1307,7 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1361,7 +1327,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -1372,7 +1338,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1443,7 +1409,7 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1462,50 +1428,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/task305/golden/marrable_site_appraisal_2027.xlsx
+++ b/task305/golden/marrable_site_appraisal_2027.xlsx
@@ -87,7 +87,7 @@
     <t>Brackenmere, Northfield</t>
   </si>
   <si>
-    <t>Addition = 26% of the store's sales, less 26% of the sales it takes from our ten stores, less its running costs (Finance's appraisal rule, spend-share model sheet). Sales include the guests of the region's holiday parks at GBP 2,480 a pitch a season; the residents-only column leaves them out.</t>
+    <t>Addition = 26% of the store's sales, less 26% of the sales it takes from our ten stores, less its running costs (Finance's appraisal rule, spend-share model sheet). Sales include the guests of the region's holiday parks at GBP 2,550 a pitch a season; the residents-only column leaves them out.</t>
   </si>
   <si>
     <t>Four pitch-measured sites on the 2026 rating list; Wrentoft Lakes is the largest</t>
@@ -120,7 +120,7 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Guests' in-store spend: GBP 2,480 a pitch for a season, from the out-of-region card spend at our stores (March to October, above each store's November to February level, grossed up by its card share).</t>
+    <t>Guests' in-store spend: GBP 2,550 a pitch for a season, from the out-of-region card spend at our stores (March to October, above each store's November to February level, grossed up by its card share).</t>
   </si>
   <si>
     <t>Guests' spend at our stores, FY2025/26</t>
@@ -718,19 +718,19 @@
         <v>1500</v>
       </c>
       <c r="D4" s="4">
-        <v>6775669</v>
+        <v>6842069</v>
       </c>
       <c r="E4" s="4">
-        <v>142674</v>
+        <v>142950</v>
       </c>
       <c r="F4" s="4">
-        <v>924000</v>
+        <v>941000</v>
       </c>
       <c r="G4" s="4">
-        <v>800579</v>
+        <v>800771</v>
       </c>
       <c r="H4" s="4">
-        <v>137306</v>
+        <v>120306</v>
       </c>
       <c r="I4" s="5">
         <v>0.8</v>
@@ -747,16 +747,16 @@
         <v>1800</v>
       </c>
       <c r="D5" s="6">
-        <v>6753698</v>
+        <v>6754870</v>
       </c>
       <c r="E5" s="6">
-        <v>612067</v>
+        <v>612127</v>
       </c>
       <c r="F5" s="6">
         <v>1177000</v>
       </c>
       <c r="G5" s="6">
-        <v>419824</v>
+        <v>420113</v>
       </c>
       <c r="H5" s="6">
         <v>408667</v>
@@ -776,16 +776,16 @@
         <v>1800</v>
       </c>
       <c r="D6" s="6">
-        <v>5235777</v>
+        <v>5235965</v>
       </c>
       <c r="E6" s="6">
-        <v>1759978</v>
+        <v>1760005</v>
       </c>
       <c r="F6" s="6">
         <v>839000</v>
       </c>
       <c r="G6" s="6">
-        <v>64708</v>
+        <v>64750</v>
       </c>
       <c r="H6" s="6">
         <v>63097</v>
@@ -805,16 +805,16 @@
         <v>1500</v>
       </c>
       <c r="D7" s="6">
-        <v>3586357</v>
+        <v>3588196</v>
       </c>
       <c r="E7" s="6">
-        <v>1180141</v>
+        <v>1180442</v>
       </c>
       <c r="F7" s="6">
         <v>662000</v>
       </c>
       <c r="G7" s="6">
-        <v>-36384</v>
+        <v>-35984</v>
       </c>
       <c r="H7" s="6">
         <v>-51802</v>
@@ -834,16 +834,16 @@
         <v>1600</v>
       </c>
       <c r="D8" s="6">
-        <v>4237684</v>
+        <v>4237799</v>
       </c>
       <c r="E8" s="6">
-        <v>2173497</v>
+        <v>2173519</v>
       </c>
       <c r="F8" s="6">
         <v>659000</v>
       </c>
       <c r="G8" s="6">
-        <v>-122311</v>
+        <v>-122287</v>
       </c>
       <c r="H8" s="6">
         <v>-123247</v>
@@ -863,16 +863,16 @@
         <v>1500</v>
       </c>
       <c r="D9" s="6">
-        <v>4399247</v>
+        <v>4399262</v>
       </c>
       <c r="E9" s="6">
-        <v>2305168</v>
+        <v>2305171</v>
       </c>
       <c r="F9" s="6">
         <v>691000</v>
       </c>
       <c r="G9" s="6">
-        <v>-146540</v>
+        <v>-146536</v>
       </c>
       <c r="H9" s="6">
         <v>-146675</v>
@@ -1006,7 +1006,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="6">
-        <v>12734</v>
+        <v>11290</v>
       </c>
     </row>
     <row r="5">
@@ -1014,7 +1014,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="6">
-        <v>-474</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="6">
@@ -1022,7 +1022,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="6">
-        <v>2441</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="7">
@@ -1030,7 +1030,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="6">
-        <v>62452</v>
+        <v>63880</v>
       </c>
     </row>
     <row r="8">
@@ -1038,7 +1038,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="6">
-        <v>147547</v>
+        <v>82995</v>
       </c>
     </row>
     <row r="9">
@@ -1046,7 +1046,7 @@
         <v>42</v>
       </c>
       <c r="B9" s="6">
-        <v>-426</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -1054,7 +1054,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="6">
-        <v>285788</v>
+        <v>150230</v>
       </c>
     </row>
     <row r="11">
@@ -1062,7 +1062,7 @@
         <v>44</v>
       </c>
       <c r="B11" s="6">
-        <v>17369</v>
+        <v>13657</v>
       </c>
     </row>
     <row r="12">
@@ -1070,7 +1070,7 @@
         <v>45</v>
       </c>
       <c r="B12" s="6">
-        <v>5389</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="13">
@@ -1078,7 +1078,7 @@
         <v>46</v>
       </c>
       <c r="B13" s="6">
-        <v>189</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="15">
@@ -1118,7 +1118,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="6">
-        <v>7020</v>
+        <v>7079</v>
       </c>
     </row>
     <row r="5">
@@ -1126,7 +1126,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="6">
-        <v>6975</v>
+        <v>7001</v>
       </c>
     </row>
     <row r="6">
@@ -1134,7 +1134,7 @@
         <v>39</v>
       </c>
       <c r="B6" s="6">
-        <v>6653</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="7">
@@ -1142,7 +1142,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="6">
-        <v>4704</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="8">
@@ -1150,7 +1150,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="6">
-        <v>3828</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="9">
@@ -1158,7 +1158,7 @@
         <v>42</v>
       </c>
       <c r="B9" s="6">
-        <v>6729</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="10">
@@ -1166,7 +1166,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="6">
-        <v>3228</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="11">
@@ -1174,7 +1174,7 @@
         <v>44</v>
       </c>
       <c r="B11" s="6">
-        <v>3933</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="12">
@@ -1182,7 +1182,7 @@
         <v>45</v>
       </c>
       <c r="B12" s="6">
-        <v>3350</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="13">
@@ -1190,7 +1190,7 @@
         <v>46</v>
       </c>
       <c r="B13" s="6">
-        <v>4359</v>
+        <v>4372</v>
       </c>
     </row>
     <row r="15">
